--- a/artfynd/A 52336-2024 artfynd.xlsx
+++ b/artfynd/A 52336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126243441</v>
       </c>
       <c r="B2" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126243054</v>
       </c>
       <c r="B3" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126244059</v>
+        <v>126243406</v>
       </c>
       <c r="B4" t="n">
-        <v>91254</v>
+        <v>91692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608328</v>
+        <v>608513</v>
       </c>
       <c r="R4" t="n">
-        <v>7295173</v>
+        <v>7295269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126243406</v>
+        <v>126244059</v>
       </c>
       <c r="B5" t="n">
-        <v>91690</v>
+        <v>91256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608513</v>
+        <v>608328</v>
       </c>
       <c r="R5" t="n">
-        <v>7295269</v>
+        <v>7295173</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>126243417</v>
       </c>
       <c r="B7" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>126243085</v>
       </c>
       <c r="B8" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126242938</v>
       </c>
       <c r="B9" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,45 +1486,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126244353</v>
+        <v>126243435</v>
       </c>
       <c r="B10" t="n">
-        <v>79562</v>
+        <v>91692</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granknösen, Granknösen, Ly lm</t>
+          <t>Vitmyran, Vitmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608287</v>
+        <v>608525</v>
       </c>
       <c r="R10" t="n">
-        <v>7295235</v>
+        <v>7295061</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1591,7 @@
         <v>126242699</v>
       </c>
       <c r="B11" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,45 +1690,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126243435</v>
+        <v>126244353</v>
       </c>
       <c r="B12" t="n">
-        <v>91690</v>
+        <v>79562</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vitmyran, Vitmyran, Ly lm</t>
+          <t>Granknösen, Granknösen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>608525</v>
+        <v>608287</v>
       </c>
       <c r="R12" t="n">
-        <v>7295061</v>
+        <v>7295235</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2101,7 +2101,7 @@
         <v>126243672</v>
       </c>
       <c r="B16" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>126244471</v>
       </c>
       <c r="B17" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 52336-2024 artfynd.xlsx
+++ b/artfynd/A 52336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126243441</v>
       </c>
       <c r="B2" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126243054</v>
       </c>
       <c r="B3" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126243406</v>
       </c>
       <c r="B4" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>126244059</v>
       </c>
       <c r="B5" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>126242678</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126243417</v>
       </c>
       <c r="B7" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>126243085</v>
       </c>
       <c r="B8" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126242938</v>
       </c>
       <c r="B9" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,45 +1486,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126243435</v>
+        <v>126242699</v>
       </c>
       <c r="B10" t="n">
-        <v>91692</v>
+        <v>91260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vitmyran, Vitmyran, Ly lm</t>
+          <t>Granknösen, Granknösen, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608525</v>
+        <v>608495</v>
       </c>
       <c r="R10" t="n">
-        <v>7295061</v>
+        <v>7295474</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,45 +1588,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126242699</v>
+        <v>126243435</v>
       </c>
       <c r="B11" t="n">
-        <v>91256</v>
+        <v>91696</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granknösen, Granknösen, Ly lm</t>
+          <t>Vitmyran, Vitmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608495</v>
+        <v>608525</v>
       </c>
       <c r="R11" t="n">
-        <v>7295474</v>
+        <v>7295061</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
         <v>126244353</v>
       </c>
       <c r="B12" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>126243979</v>
       </c>
       <c r="B13" t="n">
-        <v>77937</v>
+        <v>77941</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>126242992</v>
       </c>
       <c r="B14" t="n">
-        <v>79052</v>
+        <v>79056</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>126244347</v>
       </c>
       <c r="B15" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>126243672</v>
       </c>
       <c r="B16" t="n">
-        <v>91252</v>
+        <v>91256</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>126244471</v>
       </c>
       <c r="B17" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 52336-2024 artfynd.xlsx
+++ b/artfynd/A 52336-2024 artfynd.xlsx
@@ -1588,45 +1588,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126243435</v>
+        <v>126244353</v>
       </c>
       <c r="B11" t="n">
-        <v>91696</v>
+        <v>79566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vitmyran, Vitmyran, Ly lm</t>
+          <t>Granknösen, Granknösen, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608525</v>
+        <v>608287</v>
       </c>
       <c r="R11" t="n">
-        <v>7295061</v>
+        <v>7295235</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,45 +1690,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126244353</v>
+        <v>126243435</v>
       </c>
       <c r="B12" t="n">
-        <v>79566</v>
+        <v>91696</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Granknösen, Granknösen, Ly lm</t>
+          <t>Vitmyran, Vitmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>608287</v>
+        <v>608525</v>
       </c>
       <c r="R12" t="n">
-        <v>7295235</v>
+        <v>7295061</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 52336-2024 artfynd.xlsx
+++ b/artfynd/A 52336-2024 artfynd.xlsx
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126243406</v>
+        <v>126244059</v>
       </c>
       <c r="B4" t="n">
-        <v>91696</v>
+        <v>91260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608513</v>
+        <v>608328</v>
       </c>
       <c r="R4" t="n">
-        <v>7295269</v>
+        <v>7295173</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126244059</v>
+        <v>126243406</v>
       </c>
       <c r="B5" t="n">
-        <v>91260</v>
+        <v>91696</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608328</v>
+        <v>608513</v>
       </c>
       <c r="R5" t="n">
-        <v>7295173</v>
+        <v>7295269</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1486,45 +1486,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126242699</v>
+        <v>126243435</v>
       </c>
       <c r="B10" t="n">
-        <v>91260</v>
+        <v>91696</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granknösen, Granknösen, Ly lm</t>
+          <t>Vitmyran, Vitmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608495</v>
+        <v>608525</v>
       </c>
       <c r="R10" t="n">
-        <v>7295474</v>
+        <v>7295061</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,45 +1690,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126243435</v>
+        <v>126242699</v>
       </c>
       <c r="B12" t="n">
-        <v>91696</v>
+        <v>91260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vitmyran, Vitmyran, Ly lm</t>
+          <t>Granknösen, Granknösen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>608525</v>
+        <v>608495</v>
       </c>
       <c r="R12" t="n">
-        <v>7295061</v>
+        <v>7295474</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 52336-2024 artfynd.xlsx
+++ b/artfynd/A 52336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126243441</v>
       </c>
       <c r="B2" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126243054</v>
       </c>
       <c r="B3" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126244059</v>
+        <v>126243406</v>
       </c>
       <c r="B4" t="n">
-        <v>91260</v>
+        <v>91699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608328</v>
+        <v>608513</v>
       </c>
       <c r="R4" t="n">
-        <v>7295173</v>
+        <v>7295269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126243406</v>
+        <v>126244059</v>
       </c>
       <c r="B5" t="n">
-        <v>91696</v>
+        <v>91263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608513</v>
+        <v>608328</v>
       </c>
       <c r="R5" t="n">
-        <v>7295269</v>
+        <v>7295173</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
         <v>126242678</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126243417</v>
       </c>
       <c r="B7" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>126243085</v>
       </c>
       <c r="B8" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>126242938</v>
       </c>
       <c r="B9" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>126243435</v>
       </c>
       <c r="B10" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126244353</v>
+        <v>126242699</v>
       </c>
       <c r="B11" t="n">
-        <v>79566</v>
+        <v>91263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,21 +1599,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608287</v>
+        <v>608495</v>
       </c>
       <c r="R11" t="n">
-        <v>7295235</v>
+        <v>7295474</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126242699</v>
+        <v>126244353</v>
       </c>
       <c r="B12" t="n">
-        <v>91260</v>
+        <v>79569</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,21 +1701,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>608495</v>
+        <v>608287</v>
       </c>
       <c r="R12" t="n">
-        <v>7295474</v>
+        <v>7295235</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
         <v>126243979</v>
       </c>
       <c r="B13" t="n">
-        <v>77941</v>
+        <v>77944</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>126242992</v>
       </c>
       <c r="B14" t="n">
-        <v>79056</v>
+        <v>79059</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>126244347</v>
       </c>
       <c r="B15" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>126243672</v>
       </c>
       <c r="B16" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>126244471</v>
       </c>
       <c r="B17" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 52336-2024 artfynd.xlsx
+++ b/artfynd/A 52336-2024 artfynd.xlsx
@@ -1486,45 +1486,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126243435</v>
+        <v>126244353</v>
       </c>
       <c r="B10" t="n">
-        <v>91699</v>
+        <v>79569</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vitmyran, Vitmyran, Ly lm</t>
+          <t>Granknösen, Granknösen, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608525</v>
+        <v>608287</v>
       </c>
       <c r="R10" t="n">
-        <v>7295061</v>
+        <v>7295235</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,45 +1588,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126242699</v>
+        <v>126243435</v>
       </c>
       <c r="B11" t="n">
-        <v>91263</v>
+        <v>91699</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granknösen, Granknösen, Ly lm</t>
+          <t>Vitmyran, Vitmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608495</v>
+        <v>608525</v>
       </c>
       <c r="R11" t="n">
-        <v>7295474</v>
+        <v>7295061</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126244353</v>
+        <v>126242699</v>
       </c>
       <c r="B12" t="n">
-        <v>79569</v>
+        <v>91263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,21 +1701,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>608287</v>
+        <v>608495</v>
       </c>
       <c r="R12" t="n">
-        <v>7295235</v>
+        <v>7295474</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 52336-2024 artfynd.xlsx
+++ b/artfynd/A 52336-2024 artfynd.xlsx
@@ -1486,45 +1486,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126244353</v>
+        <v>126243435</v>
       </c>
       <c r="B10" t="n">
-        <v>79569</v>
+        <v>91699</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granknösen, Granknösen, Ly lm</t>
+          <t>Vitmyran, Vitmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608287</v>
+        <v>608525</v>
       </c>
       <c r="R10" t="n">
-        <v>7295235</v>
+        <v>7295061</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,45 +1588,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126243435</v>
+        <v>126242699</v>
       </c>
       <c r="B11" t="n">
-        <v>91699</v>
+        <v>91263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vitmyran, Vitmyran, Ly lm</t>
+          <t>Granknösen, Granknösen, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608525</v>
+        <v>608495</v>
       </c>
       <c r="R11" t="n">
-        <v>7295061</v>
+        <v>7295474</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126242699</v>
+        <v>126244353</v>
       </c>
       <c r="B12" t="n">
-        <v>91263</v>
+        <v>79569</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,21 +1701,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>608495</v>
+        <v>608287</v>
       </c>
       <c r="R12" t="n">
-        <v>7295474</v>
+        <v>7295235</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 52336-2024 artfynd.xlsx
+++ b/artfynd/A 52336-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126243441</v>
+        <v>126243979</v>
       </c>
       <c r="B2" t="n">
-        <v>91245</v>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608525</v>
+        <v>608324</v>
       </c>
       <c r="R2" t="n">
-        <v>7295061</v>
+        <v>7295092</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126243054</v>
+        <v>126243417</v>
       </c>
       <c r="B3" t="n">
-        <v>91263</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granknösen, Granknösen, Ly lm</t>
+          <t>Vitmyran, Vitmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608517</v>
+        <v>608526</v>
       </c>
       <c r="R3" t="n">
-        <v>7295271</v>
+        <v>7295061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126243406</v>
+        <v>126242992</v>
       </c>
       <c r="B4" t="n">
-        <v>91699</v>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608513</v>
+        <v>608476</v>
       </c>
       <c r="R4" t="n">
-        <v>7295269</v>
+        <v>7295320</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126244059</v>
+        <v>126243085</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608328</v>
+        <v>608513</v>
       </c>
       <c r="R5" t="n">
-        <v>7295173</v>
+        <v>7295269</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126242678</v>
+        <v>126243441</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,34 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Granknösen, Granknösen, Ly lm</t>
+          <t>Vitmyran, Vitmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608502</v>
+        <v>608525</v>
       </c>
       <c r="R6" t="n">
-        <v>7295475</v>
+        <v>7295061</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1164,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1180,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126243417</v>
+        <v>126244471</v>
       </c>
       <c r="B7" t="n">
-        <v>91541</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vitmyran, Vitmyran, Ly lm</t>
+          <t>Granknösen, Granknösen, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608526</v>
+        <v>608382</v>
       </c>
       <c r="R7" t="n">
-        <v>7295061</v>
+        <v>7295339</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,45 +1287,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126243085</v>
+        <v>126243672</v>
       </c>
       <c r="B8" t="n">
-        <v>91245</v>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Granknösen, Granknösen, Ly lm</t>
+          <t>Vitmyran, Vitmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608513</v>
+        <v>608342</v>
       </c>
       <c r="R8" t="n">
-        <v>7295269</v>
+        <v>7295109</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126242938</v>
+        <v>126243406</v>
       </c>
       <c r="B9" t="n">
-        <v>91263</v>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1419,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608497</v>
+        <v>608513</v>
       </c>
       <c r="R9" t="n">
-        <v>7295367</v>
+        <v>7295269</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126244353</v>
+        <v>126243435</v>
       </c>
       <c r="B10" t="n">
-        <v>79569</v>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,34 +1502,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granknösen, Granknösen, Ly lm</t>
+          <t>Vitmyran, Vitmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608287</v>
+        <v>608525</v>
       </c>
       <c r="R10" t="n">
-        <v>7295235</v>
+        <v>7295061</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126243435</v>
+        <v>126242678</v>
       </c>
       <c r="B11" t="n">
-        <v>91699</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,34 +1604,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vitmyran, Vitmyran, Ly lm</t>
+          <t>Granknösen, Granknösen, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608525</v>
+        <v>608502</v>
       </c>
       <c r="R11" t="n">
-        <v>7295061</v>
+        <v>7295475</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,11 +1674,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Lövrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1690,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126242699</v>
+        <v>126244347</v>
       </c>
       <c r="B12" t="n">
-        <v>91263</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,21 +1701,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>608495</v>
+        <v>608287</v>
       </c>
       <c r="R12" t="n">
-        <v>7295474</v>
+        <v>7295235</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1792,10 +1792,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126243979</v>
+        <v>126244353</v>
       </c>
       <c r="B13" t="n">
-        <v>77944</v>
+        <v>79917</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1803,34 +1803,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>314</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vitmyran, Vitmyran, Ly lm</t>
+          <t>Granknösen, Granknösen, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>608324</v>
+        <v>608287</v>
       </c>
       <c r="R13" t="n">
-        <v>7295092</v>
+        <v>7295235</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,414 +1891,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>126242992</v>
-      </c>
-      <c r="B14" t="n">
-        <v>79059</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>864</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Hypogymnia bitteri</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Granknösen, Granknösen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>608476</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7295320</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>126244347</v>
-      </c>
-      <c r="B15" t="n">
-        <v>79598</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Granknösen, Granknösen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>608287</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7295235</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>126243672</v>
-      </c>
-      <c r="B16" t="n">
-        <v>91259</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Vitmyran, Vitmyran, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>608342</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7295109</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>126244471</v>
-      </c>
-      <c r="B17" t="n">
-        <v>91245</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Granknösen, Granknösen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>608382</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7295339</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Lövrik grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52336-2024 artfynd.xlsx
+++ b/artfynd/A 52336-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243979</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243417</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126242992</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243085</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243441</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126244471</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243672</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243406</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126243435</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126242678</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126244347</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,8 +1951,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126244353</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>